--- a/data/reports/UiA_Controller_DataModel_2026.xlsx
+++ b/data/reports/UiA_Controller_DataModel_2026.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Navigasjon_Arkitektur" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Executive_Cockpit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_EVM_Prosjektkontroll" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_S_Kurve_Tidsserie" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_F05_20_Avsetningskalkyle" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Compliance_Internkontroll" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dim_Project" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dim_Date" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dim_Model_Parameter" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact_EVM_Snapshots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact_UBW_Audit" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact_Travel_Audit" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact_Project_BOA" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dim_Kontoplan_2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="00_Navigasjon_Arkitektur" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_Executive_Cockpit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_EVM_Prosjektkontroll" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_S_Kurve_Tidsserie" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_F05_20_Avsetningskalkyle" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_Compliance_Internkontroll" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Dim_Project" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Dim_Date" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dim_Model_Parameter" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Fact_EVM_Snapshots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Fact_UBW_Audit" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Fact_Travel_Audit" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Fact_Project_BOA" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Dim_Kontoplan_2026" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,14 +443,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -473,14 +473,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -505,14 +505,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -537,14 +537,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -572,8 +572,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -599,8 +599,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -626,7 +626,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -641,9 +641,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -699,8 +699,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tbl_Fact_EVM" displayName="tbl_Fact_EVM" ref="A1:O14" headerRowCount="1">
-  <autoFilter ref="A1:O14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tbl_Fact_EVM" displayName="tbl_Fact_EVM" ref="A1:O4" headerRowCount="1">
+  <autoFilter ref="A1:O4"/>
   <tableColumns count="15">
     <tableColumn id="1" name="reporting_period"/>
     <tableColumn id="2" name="snapshot_timestamp"/>
@@ -1614,12 +1614,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -1714,12 +1714,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-M08</t>
+          <t>2026-M10</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04 18:42:19</t>
+          <t>2026-10-07 09:24:38</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -1731,34 +1731,34 @@
         <v>18500000</v>
       </c>
       <c r="E2" s="13" t="n">
-        <v>12333333</v>
+        <v>12000000</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>12600000</v>
+        <v>12200000</v>
       </c>
       <c r="G2" s="13" t="n">
-        <v>12100000</v>
+        <v>11800000</v>
       </c>
       <c r="H2" s="23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="I2" s="23" t="n">
         <v>1.02</v>
       </c>
       <c r="J2" s="13" t="n">
-        <v>17788461.54</v>
+        <v>17961165.05</v>
       </c>
       <c r="K2" s="13" t="n">
-        <v>17661840.12</v>
+        <v>17796573.39</v>
       </c>
       <c r="L2" s="13" t="n">
-        <v>17794980.69</v>
+        <v>17928404.67</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>711538.46</v>
+        <v>538834.95</v>
       </c>
       <c r="N2" s="23" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
@@ -1769,12 +1769,12 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-M08</t>
+          <t>2026-M10</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04 18:42:19</t>
+          <t>2026-10-07 09:24:38</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -1786,34 +1786,34 @@
         <v>8200000</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>5466667</v>
+        <v>6500000</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>4300000</v>
+        <v>5200000</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>5800000</v>
+        <v>6800000</v>
       </c>
       <c r="H3" s="23" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="I3" s="23" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="J3" s="13" t="n">
-        <v>11081081.08</v>
+        <v>10789473.68</v>
       </c>
       <c r="K3" s="13" t="n">
-        <v>12471228.19</v>
+        <v>11734210.53</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>11000000</v>
+        <v>10706250</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>-2881081.08</v>
+        <v>-2589473.68</v>
       </c>
       <c r="N3" s="23" t="n">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
@@ -1824,12 +1824,12 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-M08</t>
+          <t>2026-M10</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04 18:42:19</t>
+          <t>2026-10-07 09:24:38</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -1841,586 +1841,36 @@
         <v>45000000</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>30000000</v>
+        <v>22500000</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>27500000</v>
+        <v>21000000</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>30200000</v>
+        <v>23100000</v>
       </c>
       <c r="H4" s="23" t="n">
         <v>0.91</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="J4" s="13" t="n">
         <v>49450549.45</v>
       </c>
       <c r="K4" s="13" t="n">
-        <v>51103010.03</v>
+        <v>51458738.04</v>
       </c>
       <c r="L4" s="13" t="n">
-        <v>49388596.49</v>
+        <v>49358205.69</v>
       </c>
       <c r="M4" s="13" t="n">
         <v>-4450549.45</v>
       </c>
       <c r="N4" s="23" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>2026-M08</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-04 18:42:19</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>UM-AI-04</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>8300000</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>11428571.43</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>11288278.39</v>
-      </c>
-      <c r="L5" s="13" t="n">
-        <v>11430534.35</v>
-      </c>
-      <c r="M5" s="13" t="n">
-        <v>571428.5699999999</v>
-      </c>
-      <c r="N5" s="23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>ON TRACK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>2026-M08</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-04 18:42:19</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>UM-HEALTH-05</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>9100000</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>10400000</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>17045454.55</v>
-      </c>
-      <c r="K6" s="13" t="n">
-        <v>17767632.37</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>17059142.21</v>
-      </c>
-      <c r="M6" s="13" t="n">
-        <v>-2045454.55</v>
-      </c>
-      <c r="N6" s="23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2026-M09</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-04 19:13:42</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>UM-DEF-02</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>18500000</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>13875000</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>14100000</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="H7" s="23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I7" s="23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>17788461.54</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>17647812.97</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>17747104.25</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>711538.46</v>
-      </c>
-      <c r="N7" s="23" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>ON TRACK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>2026-M09</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-04 19:13:42</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>UM-ENG-03</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>8200000</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>6150000</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>11081081.08</v>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>12390505.89</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>11045454.55</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>-2881081.08</v>
-      </c>
-      <c r="N8" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>2026-M09</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-04 19:13:42</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>UM-FPV-01</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>33750000</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>31000000</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>33800000</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I9" s="23" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>48913043.48</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>50340642.72</v>
-      </c>
-      <c r="L9" s="13" t="n">
-        <v>49017391.3</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>-3913043.48</v>
-      </c>
-      <c r="N9" s="23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>2026-M09</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-04 19:13:42</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>UM-AI-04</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>9300000</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I10" s="23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>11320754.72</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>11272980.4</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>11361669.83</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>679245.28</v>
-      </c>
-      <c r="N10" s="23" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>ON TRACK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>2026-M09</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-04 19:13:42</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>UM-HEALTH-05</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>11250000</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>10200000</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>11600000</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I11" s="23" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>17045454.55</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>17594005.99</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>17017607.22</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>-2045454.55</v>
-      </c>
-      <c r="N11" s="23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>2026-M10</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-05 21:07:23</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>UM-DEF-02</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>18500000</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>12200000</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I12" s="23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>17961165.05</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>17796573.39</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>17928404.67</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>538834.95</v>
-      </c>
-      <c r="N12" s="23" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>ON TRACK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>2026-M10</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-05 21:07:23</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>UM-ENG-03</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>8200000</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>6800000</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I13" s="23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>10789473.68</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>11734210.53</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>10706250</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>-2589473.68</v>
-      </c>
-      <c r="N13" s="23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>2026-M10</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-05 21:07:23</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>UM-FPV-01</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>22500000</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>23100000</v>
-      </c>
-      <c r="H14" s="23" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I14" s="23" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>49450549.45</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>51458738.04</v>
-      </c>
-      <c r="L14" s="13" t="n">
-        <v>49358205.69</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>-4450549.45</v>
-      </c>
-      <c r="N14" s="23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
